--- a/input/timetable/Магистратура_Строительство.xlsx
+++ b/input/timetable/Магистратура_Строительство.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>пара</t>
   </si>
@@ -65,6 +65,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -104,6 +107,15 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Горынин Г.Л.</t>
+  </si>
+  <si>
+    <t>Самакалев С.С.</t>
+  </si>
+  <si>
+    <t>Галиев И.М.</t>
+  </si>
+  <si>
     <t>Проектирование уникальных сооружений (лек)/(пр), А216</t>
   </si>
   <si>
@@ -149,6 +161,18 @@
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ// Лидерство и командная работа при разработке и реализации проектов (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Зеленцова С.Ю.</t>
+  </si>
+  <si>
+    <t>Шамухаметова Е.С.</t>
+  </si>
+  <si>
+    <t>Сердюкова А.М./Зеленцова С.Ю.</t>
+  </si>
+  <si>
+    <t>Сердюкова А.М./Думова Т.Б.</t>
+  </si>
+  <si>
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ// Самоорганизация и саморазвитие (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -158,10 +182,16 @@
     <t>Компьютерное моделирование строительных конструкций (лек), ЭОиДОТ// Архитектура уникальных зданий и сооружений (лек), А216</t>
   </si>
   <si>
+    <t>Галиев И.М./Покатиловский Н.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Проектирование уникальных сооружений (пр), А216//  </t>
   </si>
   <si>
     <t>//Архитектура уникальных зданий и сооружений (пр), А216</t>
+  </si>
+  <si>
+    <t>Покатиловский Н.В.</t>
   </si>
   <si>
     <t>BIM-технологии в строительстве (лек)/(лаб), ЭОиДОТ</t>
@@ -268,7 +298,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,12 +317,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -363,6 +399,64 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -804,7 +898,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -847,28 +941,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -886,161 +983,172 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1350,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1359,12 +1467,13 @@
     <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="9.28515625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.28515625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1372,15 +1481,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,39 +1497,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -1430,46 +1539,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>18</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="51"/>
+        <v>28</v>
+      </c>
+      <c r="C9" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="87"/>
       <c r="E9" s="17"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>0</v>
@@ -1480,269 +1589,318 @@
       <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="23"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="G10" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="26">
         <v>6</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="94"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="34"/>
+    </row>
+    <row r="12" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>7</v>
       </c>
-      <c r="C12" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
-    </row>
-    <row r="13" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C12" s="106" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>8</v>
       </c>
-      <c r="C13" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="54"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="C13" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="89"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="26">
         <v>6</v>
       </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="C14" s="97"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="32"/>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
         <v>7</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="100" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="47"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29">
+    </row>
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="33"/>
+      <c r="B16" s="30">
         <v>8</v>
       </c>
-      <c r="C16" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="66"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="25">
+      <c r="C16" s="103" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="26">
         <v>6</v>
       </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="57"/>
-    </row>
-    <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="C17" s="91"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="51"/>
+    </row>
+    <row r="18" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28">
         <v>7</v>
       </c>
-      <c r="C18" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="31"/>
-      <c r="B19" s="29">
+      <c r="C18" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="101"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="33"/>
+      <c r="B19" s="30">
         <v>8</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="84" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="26">
+        <v>6</v>
+      </c>
+      <c r="C20" s="66"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="51"/>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28">
+        <v>7</v>
+      </c>
+      <c r="C21" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="33"/>
+      <c r="B22" s="30">
+        <v>8</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="50">
+        <v>6</v>
+      </c>
+      <c r="C23" s="60"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="35"/>
+      <c r="B24" s="28">
+        <v>7</v>
+      </c>
+      <c r="C24" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="56" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="36"/>
+      <c r="B25" s="30">
+        <v>8</v>
+      </c>
+      <c r="C25" s="84" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="48"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="38"/>
+      <c r="B27" s="28">
+        <v>2</v>
+      </c>
+      <c r="C27" s="63"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="49"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="39"/>
+      <c r="B28" s="40">
+        <v>3</v>
+      </c>
+      <c r="C28" s="81"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="49"/>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40">
+        <v>4</v>
+      </c>
+      <c r="C29" s="72"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="49"/>
+    </row>
+    <row r="30" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="45"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="47"/>
+    </row>
+    <row r="31" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="43"/>
+      <c r="B31" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="50"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="25">
-        <v>6</v>
-      </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
-        <v>7</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="47"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="31"/>
-      <c r="B22" s="29">
-        <v>8</v>
-      </c>
-      <c r="C22" s="48" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="41"/>
+      <c r="B32" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="44">
-        <v>6</v>
-      </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="75"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="32"/>
-      <c r="B24" s="27">
-        <v>7</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="33"/>
-      <c r="B25" s="29">
-        <v>8</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="25">
-        <v>1</v>
-      </c>
-      <c r="C26" s="91" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="35"/>
-      <c r="B27" s="27">
-        <v>2</v>
-      </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="78"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="37">
-        <v>3</v>
-      </c>
-      <c r="C28" s="94"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="96"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37">
-        <v>4</v>
-      </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="87"/>
-    </row>
-    <row r="30" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="42"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="84"/>
-    </row>
-    <row r="31" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="88" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="90"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="38"/>
-      <c r="B32" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1750,11 +1908,24 @@
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C27:F27"/>
@@ -1765,19 +1936,6 @@
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E8 C9 E9">
     <cfRule type="expression" priority="2">
